--- a/TESTS/zlit_7_hrin.xlsx
+++ b/TESTS/zlit_7_hrin.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Олександр Грін — російський письменник-романтик відомий своєю «феєрією» про мрію і диво</t>
+          <t>Олександр Грін</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>«Феєрія» — так сам Грін назвав твір; це романтична повість-казка де мрія стає реальністю</t>
+          <t>«Феєрія»</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>У вигаданій країні Грінландії — Гріну властивий власний казковий географічний простір</t>
+          <t>У вигаданій країні Грінландії</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Ассоль — маленька дівчинка якій мандрівний казкар Егль пророкує що одного дня прийде корабель з пурпуровими вітрилами</t>
+          <t>Ассоль</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Воно стало сенсом її життя — Ассоль вірить у пурпурові вітрила і ця віра рятує її від відчаю</t>
+          <t>Воно стало сенсом її життя</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Насмішки і зневага — її називають «навіженою» бо мрійники незрозумілі практичним людям</t>
+          <t>Насмішки і зневага</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Молодий капітан з аристократичної родини що обрав море і мрію — він втілює пророцтво у реальність</t>
+          <t>Молодий капітан з аристократичної родини що обрав море і мрію</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Він почув про неї в таверні — і щось у цій розповіді глибоко торкнулось його серця</t>
+          <t>Він почув про неї в таверні</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -939,6 +984,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Де живе Ассоль з батьком і яке їхнє становище у суспільстві?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У великому місті, вони багаті</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У рибальському селі Каперна, де їх не люблять і зневажають</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У замку на горі</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>На кораблі</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Через що мешканці Каперни не любили Лонгрена — батька Ассоль?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він крав</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він колись відмовив у допомозі людині, що виганяла дружину його, і та людина загинула — і про це всі знали</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він був чужинцем</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він лаявся</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Чому і Ассоль зневажали в Каперні?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вона була злою</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Як дочка Лонгрена і як дівчинка, яка вірила у пророцтво і відкрито говорила про нього</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вона не вміла рибалити</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона не любила дітей</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Що старий збирач пісень Егль розповів маленькій Ассоль?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Казку про рибалку</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Пророцтво: одного дня за нею приплине корабель з пурпуровими вітрилами і красивий принц забере її</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Легенду про скарби</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Про небезпеку моря</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Скільки часу Ассоль зберігала віру у пророцтво?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Кілька місяців</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Роки — попри постійні глузування односельців, вона вірила все дитинство і юність</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Один тиждень</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона одразу забула про нього</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Яку образу Ассоль найбільш боляче ранила серед усіх насмішок?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Глузування дітей</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Образна кличка «Корабельна Ассоль» — люди відкрито сміялись над її вірою у дива</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Недружні погляди</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Тиша і ігнорування</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>У якому місті Артур Грей вперше почув про дивну дівчину з Каперни?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>У Лісі</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У портовому місті під час стоянки корабля, у таверні від матроса</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>У Каперні самій</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>У столиці</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Що Грей зробив, вранці прийшовши до узбережжя Каперни?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Одразу поплив геть</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Сховався в очереті й довго спостерігав за сплячою Ассоль, яку вперше побачив</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Поговорив з мешканцями</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Купив рибу</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Яку деталь Грей помітив на пальці сплячої Ассоль, яка вразила його?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Каблучку</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Нічого — але він залишив на її пальці своє кільце та пішов, не збудивши її</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Порізаний палець</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Татуювання</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Де Грей купив пурпурову тканину для вітрил?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Замовив її зшити</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У торговця у місті, вибравши найяскравіший, найглибший червоно-пурпурний колір</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Знайшов на кораблі</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вкрав її</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Як команда Грея поставилась до незвичайного наказу капітана — пофарбувати вітрила в пурпур?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Відмовились одразу</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони теж були романтиками і підтримали капітана з радістю</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони відверто сміялись</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони не зрозуміли наказу</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Що відчули мешканці Каперни, побачивши пурпурний корабель на горизонті?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Байдужість</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Подив і збентеження — більшість не могла пояснити явище, тоді як Ассоль впізнала своє пророцтво</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Радість і гордість</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони нічого не помітили</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Яким чином Ассоль дізналась, що корабель з пурпуровими вітрилами справді прийшов?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Їй повідомив батько</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона сама побігла на берег, почувши гомін і крики мешканців</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Їй приснився сон</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Їй написали листа</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Як Ассоль почувалась, підпливаючи на шлюпці до корабля Грея?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Злякалась і захотіла повернутись</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Переповнена щастям і тихим захопленням — мрія, у яку всі не вірили, справдилась</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Спокійно, як завжди</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вона не повірила, що це справжнє</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Що побачили мешканці Каперни, коли Ассоль пішла до корабля?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони не бачили нічого особливого</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Те саме диво, у яке вони роками не вірили і сміялись — і не змогли нічого сказати</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сміялись і кричали образи</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Плакали від щастя за неї</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що Грін хотів показати через поведінку Лонгрена після трагедії з дружиною?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Що він злодій</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Що людина, яку зламало горе і зрада суспільства, може стати замкнутою — але не злою</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Що він не любив доньку</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Що він планував помсту</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Яку іграшку Лонгрен майстрував для Ассоль у їхній бідній хатині?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ляльок</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Маленькі кораблики з різнокольоровими вітрилами, що стали першим образом майбутнього дива</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дерев'яних звірів</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Кубики</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Чому кораблики Лонгрена мають особливе символічне значення у творі?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони просто іграшки</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони стали першим зерном мрії Ассоль — від батькової любові й майстерності виросло пророцтво про вітрила</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони продавались за гроші</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони не мають жодного значення</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Яку думку про дива стверджує Грін через вибір Грея?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Дива трапляються самі собою</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Дива не чекають — їх створюють власними руками люди, здатні до великого почуття</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дива неможливі для звичайних людей</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Дива трапляються лише з обраними</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>У чому різниця між мешканцями Каперни і Греєм у ставленні до мрії?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Мешканці теж мріяли</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Мешканці зневажали мрію, вважаючи її дурницею; Грей — втілив чужу мрію своїми зусиллями</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Грей теж сміявся спочатку</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Різниці нема — всі хотіли того ж</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Що означає жанрове визначення «феєрія», яким Грін назвав свій твір?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Науково-фантастичний роман</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Казково-романтична поема у прозі, де мрія і реальність межують між собою</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Детективна історія</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Реалістичний нарис</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що таке «гринландія» і яке її значення?</t>
+          <t>«Гринландія» — власний умовний художній світ Гріна, у якому розгортаються його романтичні твори.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яким є авторський стиль Гріна?</t>
+          <t>Авторський стиль Гріна поєднує романтичний пафос мрії з точним психологічним портретом персонажів.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Яку позицію займає «Пурпурові вітрила» у світовій романтичній прозі?</t>
+          <t>«Пурпурові вітрила» Гріна є суто реалістичним побутовим романом без жодних романтичних рис.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея «Пурпурових вітрил»?</t>
+          <t>Головна ідея «Пурпурових вітрил» — дива не трапляються самі: їх творять люди здатні на велике почуття.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Що символізує протиставлення Ассоль і мешканців села?</t>
+          <t>Ассоль є символом самотнього мрійника серед практичних людей, що зневажають уяву і мрію.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яку думку про дива висловлює Грін своїм твором?</t>
+          <t>Грін стверджує, що мрія — слабкість, і краще бути реалістом, як мешканці Каперни.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які теми розкриває «Пурпурові вітрила»?</t>
+          <t>Що сталося в «Пурпурових вітрилах»?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Сила мрії і вірності</t>
+          <t>Грей залишив кільце на пальці сплячої Ассоль</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Самотність мрійника серед практичних людей</t>
+          <t>Грей наказав пофарбувати вітрила в пурпур</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Небезпека моря</t>
+          <t>Ассоль відреклась від мрії</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Здатність людини творити диво для іншої</t>
+          <t>Мешканці Каперни вийшли зустрічати корабель з радістю</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Символ здійсненної мрії — коли людина сильно вірить і інша людина захоче цю мрію здійснити</t>
+          <t>Символ здійсненної мрії</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Мрія здійснюється — це не гірка проза а феєрія де диво можливе якщо вірити і якщо є людина готова його зробити</t>
+          <t>Мрія здійснюється</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ніжного захисника і першого джерела казки — він кораблебудівник і навчив доньку вірити в диво</t>
+          <t>Ніжного захисника і першого джерела казки</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
